--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128346603</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128346601</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128346603</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128346601</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128346603</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128346601</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128346603</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128346601</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128346603</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128346601</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128346603</v>
+        <v>128346637</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468644</v>
+        <v>468853</v>
       </c>
       <c r="R2" t="n">
-        <v>7077908</v>
+        <v>7077876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128346601</v>
+        <v>128346640</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468612</v>
+        <v>468660</v>
       </c>
       <c r="R3" t="n">
-        <v>7077893</v>
+        <v>7077931</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +845,6 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,6 +866,1123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128346577</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468499</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128346581</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>468873</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7077929</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128346595</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468528</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7077863</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128346598</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468537</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7077866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128346599</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468555</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7077870</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128346600</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468599</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7077887</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128346601</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468612</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7077893</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128346602</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468636</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7077880</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128346603</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468644</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128346604</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>468658</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7077925</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128346607</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>468839</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7077932</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128346581</v>
+        <v>135192148</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468873</v>
+        <v>469354</v>
       </c>
       <c r="R5" t="n">
-        <v>7077929</v>
+        <v>7077833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,17 +1031,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128346595</v>
+        <v>128346581</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1103,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468528</v>
+        <v>468873</v>
       </c>
       <c r="R6" t="n">
-        <v>7077863</v>
+        <v>7077929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128346598</v>
+        <v>128346595</v>
       </c>
       <c r="B7" t="n">
         <v>57953</v>
@@ -1205,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468537</v>
+        <v>468528</v>
       </c>
       <c r="R7" t="n">
-        <v>7077866</v>
+        <v>7077863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128346599</v>
+        <v>128346598</v>
       </c>
       <c r="B8" t="n">
         <v>57953</v>
@@ -1307,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468555</v>
+        <v>468537</v>
       </c>
       <c r="R8" t="n">
-        <v>7077870</v>
+        <v>7077866</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128346600</v>
+        <v>128346599</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468599</v>
+        <v>468555</v>
       </c>
       <c r="R9" t="n">
-        <v>7077887</v>
+        <v>7077870</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128346601</v>
+        <v>128346600</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1511,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468612</v>
+        <v>468599</v>
       </c>
       <c r="R10" t="n">
-        <v>7077893</v>
+        <v>7077887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128346602</v>
+        <v>128346601</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1613,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468636</v>
+        <v>468612</v>
       </c>
       <c r="R11" t="n">
-        <v>7077880</v>
+        <v>7077893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,7 +1690,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128346603</v>
+        <v>128346602</v>
       </c>
       <c r="B12" t="n">
         <v>57953</v>
@@ -1715,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468644</v>
+        <v>468636</v>
       </c>
       <c r="R12" t="n">
-        <v>7077908</v>
+        <v>7077880</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,7 +1792,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128346604</v>
+        <v>128346603</v>
       </c>
       <c r="B13" t="n">
         <v>57953</v>
@@ -1817,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468658</v>
+        <v>468644</v>
       </c>
       <c r="R13" t="n">
-        <v>7077925</v>
+        <v>7077908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128346607</v>
+        <v>128346604</v>
       </c>
       <c r="B14" t="n">
         <v>57953</v>
@@ -1919,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468839</v>
+        <v>468658</v>
       </c>
       <c r="R14" t="n">
-        <v>7077932</v>
+        <v>7077925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,6 +1993,1512 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128346607</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>468839</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7077932</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346637</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192148</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346595</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346598</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346599</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346600</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346601</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346602</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346603</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346604</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2446,6 +2531,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2797,6 +2897,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3148,6 +3263,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3265,6 +3385,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3382,6 +3507,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3499,8 +3629,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135192148</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>135192074</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135192077</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135192079</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>135192085</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135192088</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>135192093</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135192116</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135192118</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135192127</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135192128</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>135192130</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192131</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135192148</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,45 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128346581</v>
+        <v>135192148</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468873</v>
+        <v>469354</v>
       </c>
       <c r="R5" t="n">
-        <v>7077929</v>
+        <v>7077833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,17 +1051,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,13 +1097,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346581</t>
+          <t>https://artportalen.se/Sighting/135192148</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128346595</v>
+        <v>128346581</v>
       </c>
       <c r="B6" t="n">
         <v>57953</v>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468528</v>
+        <v>468873</v>
       </c>
       <c r="R6" t="n">
-        <v>7077863</v>
+        <v>7077929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,13 +1204,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346595</t>
+          <t>https://artportalen.se/Sighting/128346581</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128346598</v>
+        <v>128346595</v>
       </c>
       <c r="B7" t="n">
         <v>57953</v>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468537</v>
+        <v>468528</v>
       </c>
       <c r="R7" t="n">
-        <v>7077866</v>
+        <v>7077863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,13 +1311,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346598</t>
+          <t>https://artportalen.se/Sighting/128346595</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128346599</v>
+        <v>128346598</v>
       </c>
       <c r="B8" t="n">
         <v>57953</v>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468555</v>
+        <v>468537</v>
       </c>
       <c r="R8" t="n">
-        <v>7077870</v>
+        <v>7077866</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,13 +1418,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346599</t>
+          <t>https://artportalen.se/Sighting/128346598</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128346600</v>
+        <v>128346599</v>
       </c>
       <c r="B9" t="n">
         <v>57953</v>
@@ -1449,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468599</v>
+        <v>468555</v>
       </c>
       <c r="R9" t="n">
-        <v>7077887</v>
+        <v>7077870</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,13 +1525,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346600</t>
+          <t>https://artportalen.se/Sighting/128346599</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128346601</v>
+        <v>128346600</v>
       </c>
       <c r="B10" t="n">
         <v>57953</v>
@@ -1556,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468612</v>
+        <v>468599</v>
       </c>
       <c r="R10" t="n">
-        <v>7077893</v>
+        <v>7077887</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,13 +1632,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346601</t>
+          <t>https://artportalen.se/Sighting/128346600</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128346602</v>
+        <v>128346601</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1663,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468636</v>
+        <v>468612</v>
       </c>
       <c r="R11" t="n">
-        <v>7077880</v>
+        <v>7077893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,13 +1739,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346602</t>
+          <t>https://artportalen.se/Sighting/128346601</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128346603</v>
+        <v>128346602</v>
       </c>
       <c r="B12" t="n">
         <v>57953</v>
@@ -1770,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468644</v>
+        <v>468636</v>
       </c>
       <c r="R12" t="n">
-        <v>7077908</v>
+        <v>7077880</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,13 +1846,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346603</t>
+          <t>https://artportalen.se/Sighting/128346602</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128346604</v>
+        <v>128346603</v>
       </c>
       <c r="B13" t="n">
         <v>57953</v>
@@ -1877,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468658</v>
+        <v>468644</v>
       </c>
       <c r="R13" t="n">
-        <v>7077925</v>
+        <v>7077908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,13 +1953,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346604</t>
+          <t>https://artportalen.se/Sighting/128346603</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128346607</v>
+        <v>128346604</v>
       </c>
       <c r="B14" t="n">
         <v>57953</v>
@@ -1984,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468839</v>
+        <v>468658</v>
       </c>
       <c r="R14" t="n">
-        <v>7077932</v>
+        <v>7077925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2060,1578 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128346604</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128346607</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>468839</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7077932</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -2069,6 +3650,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,1470 +2168,6 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346607</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135192074</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>469051</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7077912</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192074</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135192077</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>469002</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192077</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135192079</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>469028</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7077856</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192079</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135192085</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>468941</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7077921</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192085</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135192088</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>468900</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7077908</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192088</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135192093</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>468841</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192093</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135192116</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>469092</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7077868</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192116</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135192118</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>469121</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192118</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135192127</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>469140</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7077913</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192127</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135192128</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>469149</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192128</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135192130</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>469158</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192130</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135192131</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>469166</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7077841</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -3651,18 +2187,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,1470 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -2187,6 +3651,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -2176,7 +2176,7 @@
         <v>135192074</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135192077</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135192079</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>135192085</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135192088</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>135192093</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135192116</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135192118</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135192127</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135192128</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>135192130</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192131</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,1470 +2168,6 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346607</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135192074</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>469051</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7077912</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192074</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135192077</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>469002</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192077</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135192079</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>469028</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7077856</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192079</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135192085</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>468941</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7077921</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192085</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135192088</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>468900</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7077908</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192088</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135192093</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>468841</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192093</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135192116</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>469092</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7077868</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192116</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135192118</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>469121</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192118</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135192127</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>469140</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7077913</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192127</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135192128</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>469149</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192128</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135192130</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>469158</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192130</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135192131</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>469166</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7077841</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -3651,18 +2187,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,1470 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -2187,6 +3651,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -2176,7 +2176,7 @@
         <v>135192074</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135192077</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135192079</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>135192085</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135192088</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>135192093</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135192116</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135192118</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135192127</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135192128</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>135192130</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192131</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -2176,7 +2176,7 @@
         <v>135192074</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135192077</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135192079</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>135192085</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135192088</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>135192093</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135192116</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135192118</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135192127</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135192128</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>135192130</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192131</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -2176,7 +2176,7 @@
         <v>135192074</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135192077</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135192079</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>135192085</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135192088</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>135192093</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135192116</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135192118</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135192127</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135192128</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>135192130</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192131</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -2176,7 +2176,7 @@
         <v>135192074</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>135192077</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>135192079</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>135192085</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135192088</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>135192093</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135192116</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135192118</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135192127</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135192128</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>135192130</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192131</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,1470 +2168,6 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346607</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>135192074</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>469051</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7077912</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192074</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>135192077</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>469002</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192077</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135192079</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>469028</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7077856</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192079</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135192085</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>468941</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7077921</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192085</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135192088</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>468900</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7077908</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192088</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135192093</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>468841</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192093</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135192116</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>469092</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7077868</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192116</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135192118</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>469121</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192118</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135192127</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>469140</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7077913</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192127</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135192128</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>469149</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192128</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135192130</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>469158</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192130</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135192131</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>469166</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7077841</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -3651,18 +2187,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25268-2025 artfynd.xlsx
+++ b/artfynd/A 25268-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,1470 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
         </is>
       </c>
     </row>
@@ -2187,6 +3651,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
